--- a/templates/ebilanz-template.xlsx
+++ b/templates/ebilanz-template.xlsx
@@ -979,6 +979,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" errorStyle="stop" allowBlank="0" showDropDown="0" showInputMessage="1" showErrorMessage="1" promptTitle="Rechtsform" prompt="GmbH: gezeichnetes Kapital mindestens 25.000 EUR.&#10;UG (haftungsbeschränkt): mindestens 1 EUR; gesetzliche Rücklage von 25 % des Jahresüberschusses nach § 5a Abs. 3 GmbHG beachten." errorTitle="Ungültige Rechtsform" error="Bitte eine Rechtsform aus der Liste wählen: GmbH oder UG (haftungsbeschränkt)." sqref="B6">
+      <formula1>"GmbH,UG (haftungsbeschränkt)"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
